--- a/artfynd/A 17762-2024 artfynd.xlsx
+++ b/artfynd/A 17762-2024 artfynd.xlsx
@@ -4867,7 +4867,7 @@
         <v>117170372</v>
       </c>
       <c r="B38" t="n">
-        <v>106308</v>
+        <v>106627</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 17762-2024 artfynd.xlsx
+++ b/artfynd/A 17762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>233570</v>
+        <v>213815</v>
       </c>
       <c r="B2" t="n">
-        <v>88844</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>682</v>
+        <v>599</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Naveljordstjärna</t>
+          <t>Grönnopping</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum elegans</t>
+          <t>Entoloma incanum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Vittad.</t>
+          <t>(Fr.) Hesler</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ölbäck, Gtl</t>
+          <t>Ölback, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700839.7783546303</v>
+        <v>700840</v>
       </c>
       <c r="R2" t="n">
-        <v>6391732.83568886</v>
+        <v>6391733</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-09-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -777,19 +762,9 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>under Pinus sylvestris, rich soil</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>SLU Artdatabanken</t>
-        </is>
-      </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>J.C. Zamora</t>
+          <t>Ingen samling</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,67 +786,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68473016</v>
+        <v>233570</v>
       </c>
       <c r="B3" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3674</v>
+        <v>682</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Naveljordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Geastrum elegans</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Vittad.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37, Gtl</t>
+          <t>Ölbäck, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700874.5436031924</v>
+        <v>700840</v>
       </c>
       <c r="R3" t="n">
-        <v>6391606.349151416</v>
+        <v>6391733</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,22 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-11-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-11-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>leg. E. Bohus-Jensen &amp; leg. J.C. Zamora</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,72 +870,99 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>under Pinus sylvestris, rich soil</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>SLU Artdatabanken</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>J.C. Zamora</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Overmark</t>
+          <t>Ibai Olariaga</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Overmark</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Elsa Bohus Jensen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>NMC - Nordic Mycological Congress</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1088797</v>
+        <v>117170372</v>
       </c>
       <c r="B4" t="n">
-        <v>86129</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107690</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2016</v>
+        <v>872</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kalkvaxskivling</t>
+          <t>Järnek</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrocybe calciphila</t>
+          <t>Ilex aquifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Arnolds</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ölbäck, Gtl</t>
+          <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700839.7783546303</v>
+        <v>700960</v>
       </c>
       <c r="R4" t="n">
-        <v>6391732.83568886</v>
+        <v>6391662</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,27 +986,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-09-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>leg. J.C. Zamora</t>
+          <t>Två stammar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,43 +1010,28 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>alvar ground</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr"/>
+          <t>Sandtallskog.</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ibai Olariaga</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Ibai Olariaga</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>NMC - Nordic Mycological Congress</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117170382</v>
+        <v>1088797</v>
       </c>
       <c r="B5" t="n">
-        <v>108669</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,37 +1039,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>2016</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kalkvaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hygrocybe calciphila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Arnolds</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Ölbäck, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700829</v>
+        <v>700840</v>
       </c>
       <c r="R5" t="n">
-        <v>6391575</v>
+        <v>6391733</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1140,17 +1093,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2011-09-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2011-09-28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka. Pyrola sp. spridd i skogen.</t>
+          <t>leg. J.C. Zamora</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,55 +1117,60 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Blåbärstallskog.</t>
-        </is>
-      </c>
+          <t>alvar ground</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ibai Olariaga</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Ibai Olariaga</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>NMC - Nordic Mycological Congress</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117170408</v>
+        <v>117170418</v>
       </c>
       <c r="B6" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220164</v>
+        <v>2078</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Gråfingerört</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Potentilla incana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>G. Gaertn., B. Mey. &amp; Scherb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1222,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700839</v>
+        <v>700823</v>
       </c>
       <c r="R6" t="n">
-        <v>6391685</v>
+        <v>6391679</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1262,7 +1220,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Alvarglänta 15 m x 10 m i V-O.</t>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,53 +1252,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117170377</v>
+        <v>117170419</v>
       </c>
       <c r="B7" t="n">
-        <v>108669</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>2078</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gråfingerört</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Potentilla incana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>G. Gaertn., B. Mey. &amp; Scherb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700956</v>
+        <v>700819</v>
       </c>
       <c r="R7" t="n">
-        <v>6391629</v>
+        <v>6391683</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,7 +1341,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,7 +1355,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Sandtallskog.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1406,50 +1373,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117170395</v>
+        <v>117170492</v>
       </c>
       <c r="B8" t="n">
-        <v>106075</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221849</v>
+        <v>2078</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gråfingerört</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Potentilla incana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>G. Gaertn., B. Mey. &amp; Scherb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700743</v>
+        <v>700913</v>
       </c>
       <c r="R8" t="n">
-        <v>6391617</v>
+        <v>6391766</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1484,6 +1455,11 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kalktallskog gles mot S</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1492,6 +1468,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,53 +1489,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117170437</v>
+        <v>68473004</v>
       </c>
       <c r="B9" t="n">
-        <v>106075</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221849</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700821</v>
+        <v>700975</v>
       </c>
       <c r="R9" t="n">
-        <v>6391712</v>
+        <v>6391674</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,17 +1568,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2017-11-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Alvarglänta 15 m x 5 m.</t>
+          <t>2017-11-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,76 +1582,81 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Amanda Overmark</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Amanda Overmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117170409</v>
+        <v>68473016</v>
       </c>
       <c r="B10" t="n">
-        <v>106075</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221849</v>
+        <v>3674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700839</v>
+        <v>700875</v>
       </c>
       <c r="R10" t="n">
-        <v>6391685</v>
+        <v>6391606</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,17 +1680,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2017-11-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Alvarglänta 15 m x 10 m i V-O. Rikligt.</t>
+          <t>2017-11-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,90 +1694,72 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Amanda Overmark</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Amanda Overmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117170350</v>
+        <v>120661214</v>
       </c>
       <c r="B11" t="n">
-        <v>98452</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222309</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Stadshajden, Stadshajden, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700953</v>
+        <v>701034</v>
       </c>
       <c r="R11" t="n">
-        <v>6391726</v>
+        <v>6391696</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1816,12 +1783,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,65 +1797,56 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117170441</v>
+        <v>117170323</v>
       </c>
       <c r="B12" t="n">
-        <v>106821</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223700</v>
+        <v>219864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hällklofibbla</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crepis tectorum var. glabrescens</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Neuman</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1907,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700821</v>
+        <v>700939</v>
       </c>
       <c r="R12" t="n">
-        <v>6391742</v>
+        <v>6391760</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1945,11 +1903,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Karstsprickor 10 cm breda.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1961,7 +1914,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Alvar , kalkkarstspricka vid.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1979,15 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117170476</v>
+        <v>117170330</v>
       </c>
       <c r="B13" t="n">
-        <v>97830</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +1962,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2033,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700894</v>
+        <v>700967</v>
       </c>
       <c r="R13" t="n">
-        <v>6391731</v>
+        <v>6391754</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2071,6 +2019,11 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Alvar 40 m x 40 m mot landsväg.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2082,7 +2035,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Alvar , kalkglänta, sand över kalk.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2100,53 +2053,62 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117170470</v>
+        <v>117170334</v>
       </c>
       <c r="B14" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220164</v>
+        <v>219864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700886</v>
+        <v>700959</v>
       </c>
       <c r="R14" t="n">
-        <v>6391729</v>
+        <v>6391753</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2178,11 +2140,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kalkhällglänta 35 x 10 m.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2194,7 +2151,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Alvar , kalkhällglänta.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2212,32 +2169,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117170401</v>
+        <v>117170337</v>
       </c>
       <c r="B15" t="n">
-        <v>108669</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2247,17 +2199,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2266,13 +2218,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700781</v>
+        <v>700952</v>
       </c>
       <c r="R15" t="n">
-        <v>6391656</v>
+        <v>6391748</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2315,7 +2267,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Tallskog, gammal, på förmodat sandunderlag.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2333,42 +2285,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117170346</v>
+        <v>117170345</v>
       </c>
       <c r="B16" t="n">
-        <v>98452</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222309</v>
+        <v>219864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2459,15 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117170467</v>
+        <v>117170389</v>
       </c>
       <c r="B17" t="n">
-        <v>100063</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,37 +2417,51 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>219864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700887</v>
+        <v>700737</v>
       </c>
       <c r="R17" t="n">
-        <v>6391723</v>
+        <v>6391563</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2548,7 +2504,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Alvar , kalkkarstspricka.</t>
+          <t>Älväxingglänta övergång mot tallskog på sand.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2566,50 +2522,59 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117170418</v>
+        <v>117170459</v>
       </c>
       <c r="B18" t="n">
-        <v>101577</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2078</v>
+        <v>219864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gråfingerört</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Potentilla incana</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>G. Gaertn., B. Mey. &amp; Scherb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700823</v>
+        <v>700872</v>
       </c>
       <c r="R18" t="n">
-        <v>6391679</v>
+        <v>6391711</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2642,11 +2607,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2678,42 +2638,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117170352</v>
+        <v>117170460</v>
       </c>
       <c r="B19" t="n">
-        <v>98452</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222309</v>
+        <v>219864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2732,10 +2687,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700946</v>
+        <v>700880</v>
       </c>
       <c r="R19" t="n">
-        <v>6391715</v>
+        <v>6391713</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2799,42 +2754,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117170351</v>
+        <v>117170463</v>
       </c>
       <c r="B20" t="n">
-        <v>98452</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222309</v>
+        <v>219864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2853,10 +2803,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700950</v>
+        <v>700891</v>
       </c>
       <c r="R20" t="n">
-        <v>6391720</v>
+        <v>6391713</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2920,53 +2870,62 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117170453</v>
+        <v>117170471</v>
       </c>
       <c r="B21" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220164</v>
+        <v>219864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700867</v>
+        <v>700886</v>
       </c>
       <c r="R21" t="n">
-        <v>6391711</v>
+        <v>6391729</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2998,6 +2957,11 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Kalkhällglänta 35 x 10 m.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3009,7 +2973,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvar , kalkhällglänta.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3027,53 +2991,62 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117170480</v>
+        <v>117170476</v>
       </c>
       <c r="B22" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220164</v>
+        <v>219864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700905</v>
+        <v>700894</v>
       </c>
       <c r="R22" t="n">
-        <v>6391738</v>
+        <v>6391731</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3134,42 +3107,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117170404</v>
+        <v>117170488</v>
       </c>
       <c r="B23" t="n">
-        <v>98452</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222309</v>
+        <v>219864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3188,10 +3156,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700802</v>
+        <v>700917</v>
       </c>
       <c r="R23" t="n">
-        <v>6391676</v>
+        <v>6391754</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3237,7 +3205,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Alvarglänta i fuktstråk.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3255,32 +3223,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117170406</v>
+        <v>117170493</v>
       </c>
       <c r="B24" t="n">
-        <v>105691</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221903</v>
+        <v>219864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3288,17 +3251,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700839</v>
+        <v>700913</v>
       </c>
       <c r="R24" t="n">
-        <v>6391685</v>
+        <v>6391766</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3335,7 +3312,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Alvarglänta 15 m x 10 m i V-O.</t>
+          <t>Kalktallskog gles mot S</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3367,50 +3344,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117170343</v>
+        <v>117170390</v>
       </c>
       <c r="B25" t="n">
-        <v>106075</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221849</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700963</v>
+        <v>700720</v>
       </c>
       <c r="R25" t="n">
-        <v>6391736</v>
+        <v>6391565</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3445,11 +3431,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Alvarmark mot V och norrut mot landsväg.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3461,7 +3442,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Älväxingglänta övergång mot tallskog på sand.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3479,15 +3460,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117170428</v>
+        <v>117170329</v>
       </c>
       <c r="B26" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,13 +3495,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700808</v>
+        <v>700967</v>
       </c>
       <c r="R26" t="n">
-        <v>6391681</v>
+        <v>6391754</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3559,7 +3535,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. Ansluter till annan glänta mot N.</t>
+          <t>Alvar 40 m x 40 m mot landsväg.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3591,15 +3567,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117170415</v>
+        <v>117170336</v>
       </c>
       <c r="B27" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3631,13 +3602,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700819</v>
+        <v>700952</v>
       </c>
       <c r="R27" t="n">
-        <v>6391683</v>
+        <v>6391748</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3667,11 +3638,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3703,15 +3669,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117170421</v>
+        <v>117170340</v>
       </c>
       <c r="B28" t="n">
-        <v>106075</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,21 +3680,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3743,10 +3704,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700818</v>
+        <v>700954</v>
       </c>
       <c r="R28" t="n">
-        <v>6391690</v>
+        <v>6391743</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3779,11 +3740,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3815,15 +3771,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117170378</v>
+        <v>117170358</v>
       </c>
       <c r="B29" t="n">
-        <v>108669</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3831,21 +3782,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3855,13 +3806,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700914</v>
+        <v>701013</v>
       </c>
       <c r="R29" t="n">
-        <v>6391607</v>
+        <v>6391677</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3895,7 +3846,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Enstaka. Pyrola sp. spridd i skogen.</t>
+          <t>Undviks vid eventuell avverkning i området.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3909,7 +3860,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Blåbärstallskog.</t>
+          <t>Alvarglänta, kalkhällar.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3927,15 +3878,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117170348</v>
+        <v>117170396</v>
       </c>
       <c r="B30" t="n">
-        <v>98452</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3943,48 +3889,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222309</v>
+        <v>220164</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700958</v>
+        <v>700743</v>
       </c>
       <c r="R30" t="n">
-        <v>6391731</v>
+        <v>6391617</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4027,11 +3959,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4048,15 +3975,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117170434</v>
+        <v>117170408</v>
       </c>
       <c r="B31" t="n">
-        <v>106075</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,21 +3986,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4088,13 +4010,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700804</v>
+        <v>700839</v>
       </c>
       <c r="R31" t="n">
-        <v>6391694</v>
+        <v>6391685</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4128,7 +4050,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Alvarglänta i båge mot O, 45 m x 15 m.</t>
+          <t>Alvarglänta 15 m x 10 m i V-O.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4160,15 +4082,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117170436</v>
+        <v>117170410</v>
       </c>
       <c r="B32" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4200,10 +4117,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700804</v>
+        <v>700828</v>
       </c>
       <c r="R32" t="n">
-        <v>6391694</v>
+        <v>6391684</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4240,7 +4157,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Alvarglänta i båge mot O, 45 m x 15 m.</t>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4272,15 +4189,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117170427</v>
+        <v>117170415</v>
       </c>
       <c r="B33" t="n">
-        <v>98452</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,48 +4200,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222309</v>
+        <v>220164</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700793</v>
+        <v>700819</v>
       </c>
       <c r="R33" t="n">
-        <v>6391685</v>
+        <v>6391683</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4366,7 +4264,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. Ansluter till annan glänta mot N. i V-hörn av gläntan.</t>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4398,15 +4296,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117170405</v>
+        <v>117170428</v>
       </c>
       <c r="B34" t="n">
-        <v>98452</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4414,21 +4307,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222309</v>
+        <v>220164</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4438,13 +4331,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700839</v>
+        <v>700808</v>
       </c>
       <c r="R34" t="n">
-        <v>6391685</v>
+        <v>6391681</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4478,7 +4371,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Alvarglänta 15 m x 10 m i V-O.</t>
+          <t>Alvarglänta 50 m x 20 m i V-O. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4510,67 +4403,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117170419</v>
+        <v>117170436</v>
       </c>
       <c r="B35" t="n">
-        <v>101577</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2078</v>
+        <v>220164</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gråfingerört</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Potentilla incana</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>G. Gaertn., B. Mey. &amp; Scherb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700819</v>
+        <v>700804</v>
       </c>
       <c r="R35" t="n">
-        <v>6391683</v>
+        <v>6391694</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4604,7 +4478,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+          <t>Alvarglänta i båge mot O, 45 m x 15 m.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4636,64 +4510,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117170459</v>
+        <v>117170438</v>
       </c>
       <c r="B36" t="n">
-        <v>97830</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219864</v>
+        <v>220164</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700872</v>
+        <v>700821</v>
       </c>
       <c r="R36" t="n">
-        <v>6391711</v>
+        <v>6391712</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4726,6 +4581,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Alvarglänta 15 m x 5 m.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4757,15 +4617,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117170454</v>
+        <v>117170447</v>
       </c>
       <c r="B37" t="n">
-        <v>106075</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4773,21 +4628,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4797,13 +4652,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700867</v>
+        <v>700827</v>
       </c>
       <c r="R37" t="n">
-        <v>6391711</v>
+        <v>6391746</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4833,6 +4688,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Alvasrglänta på kalk: 15 m x 15 m. Karst i NO.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4864,64 +4724,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117170372</v>
+        <v>117170453</v>
       </c>
       <c r="B38" t="n">
-        <v>106653</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>872</v>
+        <v>220164</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järnek</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ilex aquifolium</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700960</v>
+        <v>700867</v>
       </c>
       <c r="R38" t="n">
-        <v>6391662</v>
+        <v>6391711</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4956,11 +4797,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Två stammar.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4972,7 +4808,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Sandtallskog.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4990,15 +4826,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117170417</v>
+        <v>117170458</v>
       </c>
       <c r="B39" t="n">
-        <v>98452</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5006,21 +4837,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222309</v>
+        <v>220164</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5030,10 +4861,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700823</v>
+        <v>700872</v>
       </c>
       <c r="R39" t="n">
-        <v>6391679</v>
+        <v>6391711</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5066,11 +4897,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5102,15 +4928,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117170475</v>
+        <v>117170462</v>
       </c>
       <c r="B40" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5142,10 +4963,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700894</v>
+        <v>700891</v>
       </c>
       <c r="R40" t="n">
-        <v>6391731</v>
+        <v>6391713</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5191,7 +5012,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Alvar , kalkglänta, sand över kalk.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5209,15 +5030,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117170462</v>
+        <v>117170470</v>
       </c>
       <c r="B41" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5249,13 +5065,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700891</v>
+        <v>700886</v>
       </c>
       <c r="R41" t="n">
-        <v>6391713</v>
+        <v>6391729</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5287,6 +5103,11 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Kalkhällglänta 35 x 10 m.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5298,7 +5119,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvar , kalkhällglänta.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5316,15 +5137,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117170420</v>
+        <v>117170475</v>
       </c>
       <c r="B42" t="n">
-        <v>98452</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5332,21 +5148,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222309</v>
+        <v>220164</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5356,10 +5172,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700818</v>
+        <v>700894</v>
       </c>
       <c r="R42" t="n">
-        <v>6391690</v>
+        <v>6391731</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5394,11 +5210,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5410,7 +5221,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvar , kalkglänta, sand över kalk.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5428,15 +5239,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117170373</v>
+        <v>117170480</v>
       </c>
       <c r="B43" t="n">
-        <v>108669</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5444,21 +5250,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5468,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700948</v>
+        <v>700905</v>
       </c>
       <c r="R43" t="n">
-        <v>6391643</v>
+        <v>6391738</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5506,11 +5312,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5522,7 +5323,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Sandtallskog.</t>
+          <t>Alvar , kalkglänta, sand över kalk.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5540,15 +5341,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117170447</v>
+        <v>117170486</v>
       </c>
       <c r="B44" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5580,13 +5376,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700827</v>
+        <v>700917</v>
       </c>
       <c r="R44" t="n">
-        <v>6391746</v>
+        <v>6391754</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5616,11 +5412,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Alvasrglänta på kalk: 15 m x 15 m. Karst i NO.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5652,32 +5443,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117170463</v>
+        <v>117170370</v>
       </c>
       <c r="B45" t="n">
-        <v>97830</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5685,34 +5471,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>700891</v>
+        <v>700955</v>
       </c>
       <c r="R45" t="n">
-        <v>6391713</v>
+        <v>6391666</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5744,6 +5516,11 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5755,7 +5532,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Sandtallskog.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5773,32 +5550,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117170460</v>
+        <v>117170373</v>
       </c>
       <c r="B46" t="n">
-        <v>97830</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5806,34 +5578,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700880</v>
+        <v>700948</v>
       </c>
       <c r="R46" t="n">
-        <v>6391713</v>
+        <v>6391643</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5865,6 +5623,11 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5876,7 +5639,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Sandtallskog.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5894,15 +5657,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117170411</v>
+        <v>117170377</v>
       </c>
       <c r="B47" t="n">
-        <v>106075</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5910,16 +5668,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5934,13 +5692,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700828</v>
+        <v>700956</v>
       </c>
       <c r="R47" t="n">
-        <v>6391684</v>
+        <v>6391629</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5974,7 +5732,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5988,7 +5746,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Sandtallskog.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6006,32 +5764,27 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117170345</v>
+        <v>117170378</v>
       </c>
       <c r="B48" t="n">
-        <v>97830</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6039,34 +5792,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700963</v>
+        <v>700914</v>
       </c>
       <c r="R48" t="n">
-        <v>6391736</v>
+        <v>6391607</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6100,7 +5839,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Alvarmark mot V och norrut mot landsväg.</t>
+          <t>Enstaka. Pyrola sp. spridd i skogen.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6114,7 +5853,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Blåbärstallskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6132,15 +5871,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117170438</v>
+        <v>117170381</v>
       </c>
       <c r="B49" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,21 +5882,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220164</v>
+        <v>220299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6172,13 +5906,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700821</v>
+        <v>700877</v>
       </c>
       <c r="R49" t="n">
-        <v>6391712</v>
+        <v>6391598</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6212,7 +5946,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Alvarglänta 15 m x 5 m.</t>
+          <t>Enstaka. Pyrola sp. spridd i skogen.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6226,7 +5960,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Blåbärstallskog.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6244,15 +5978,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117170370</v>
+        <v>117170382</v>
       </c>
       <c r="B50" t="n">
-        <v>108669</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6284,10 +6013,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700955</v>
+        <v>700829</v>
       </c>
       <c r="R50" t="n">
-        <v>6391666</v>
+        <v>6391575</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6324,7 +6053,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Enstaka. Pyrola sp. spridd i skogen.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6338,7 +6067,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Sandtallskog.</t>
+          <t>Blåbärstallskog.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6356,15 +6085,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117170410</v>
+        <v>117170387</v>
       </c>
       <c r="B51" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6372,37 +6096,51 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220164</v>
+        <v>220299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700828</v>
+        <v>700737</v>
       </c>
       <c r="R51" t="n">
-        <v>6391684</v>
+        <v>6391563</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6436,7 +6174,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+          <t>Även spridd i omgivande skog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6450,7 +6188,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Tallskog, gammal, på förmodat sandunderlag.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6468,15 +6206,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117170461</v>
+        <v>117170401</v>
       </c>
       <c r="B52" t="n">
-        <v>106075</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6484,16 +6217,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6501,20 +6234,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700891</v>
+        <v>700781</v>
       </c>
       <c r="R52" t="n">
-        <v>6391713</v>
+        <v>6391656</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6557,7 +6304,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Tallskog, gammal, på förmodat sandunderlag.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6575,15 +6322,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117170429</v>
+        <v>117170335</v>
       </c>
       <c r="B53" t="n">
-        <v>106075</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6615,13 +6357,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700808</v>
+        <v>700952</v>
       </c>
       <c r="R53" t="n">
-        <v>6391681</v>
+        <v>6391748</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6651,11 +6393,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6687,15 +6424,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117170412</v>
+        <v>117170339</v>
       </c>
       <c r="B54" t="n">
-        <v>98452</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6703,48 +6435,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700828</v>
+        <v>700954</v>
       </c>
       <c r="R54" t="n">
-        <v>6391684</v>
+        <v>6391743</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6777,11 +6495,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6813,15 +6526,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117170397</v>
+        <v>117170343</v>
       </c>
       <c r="B55" t="n">
-        <v>98452</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6829,51 +6537,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700759</v>
+        <v>700963</v>
       </c>
       <c r="R55" t="n">
-        <v>6391617</v>
+        <v>6391736</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6907,7 +6601,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minsta antal. Även spridd.</t>
+          <t>Alvarmark mot V och norrut mot landsväg.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6921,7 +6615,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Sandig glänta i tallskog.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6939,15 +6633,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117170392</v>
+        <v>117170356</v>
       </c>
       <c r="B56" t="n">
-        <v>106075</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6979,13 +6668,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700737</v>
+        <v>701013</v>
       </c>
       <c r="R56" t="n">
-        <v>6391603</v>
+        <v>6391677</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7017,6 +6706,11 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Undviks vid eventuell avverkning i området.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7025,6 +6719,11 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Alvarglänta, kalkhällar.</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7041,37 +6740,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117170457</v>
+        <v>117170392</v>
       </c>
       <c r="B57" t="n">
-        <v>100063</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>221849</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7081,10 +6775,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700843</v>
+        <v>700737</v>
       </c>
       <c r="R57" t="n">
-        <v>6391731</v>
+        <v>6391603</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7127,11 +6821,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Alvar , kalkkarstspricka.</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7148,32 +6837,27 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117170471</v>
+        <v>117170395</v>
       </c>
       <c r="B58" t="n">
-        <v>97830</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219864</v>
+        <v>221849</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7181,34 +6865,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700886</v>
+        <v>700743</v>
       </c>
       <c r="R58" t="n">
-        <v>6391729</v>
+        <v>6391617</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7240,11 +6910,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Kalkhällglänta 35 x 10 m.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7253,11 +6918,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Alvar , kalkhällglänta.</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7274,15 +6934,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117170396</v>
+        <v>117170409</v>
       </c>
       <c r="B59" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7290,21 +6945,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7314,10 +6969,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700743</v>
+        <v>700839</v>
       </c>
       <c r="R59" t="n">
-        <v>6391617</v>
+        <v>6391685</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7352,6 +7007,11 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Alvarglänta 15 m x 10 m i V-O. Rikligt.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7360,6 +7020,11 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7376,15 +7041,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117170381</v>
+        <v>117170411</v>
       </c>
       <c r="B60" t="n">
-        <v>108669</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7392,16 +7052,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7416,13 +7076,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700877</v>
+        <v>700828</v>
       </c>
       <c r="R60" t="n">
-        <v>6391598</v>
+        <v>6391684</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7456,7 +7116,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Enstaka. Pyrola sp. spridd i skogen.</t>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7470,7 +7130,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Blåbärstallskog.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7488,15 +7148,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117170458</v>
+        <v>117170421</v>
       </c>
       <c r="B61" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7504,21 +7159,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7528,10 +7183,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700872</v>
+        <v>700818</v>
       </c>
       <c r="R61" t="n">
-        <v>6391711</v>
+        <v>6391690</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7564,6 +7219,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7595,15 +7255,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120660659</v>
+        <v>117170429</v>
       </c>
       <c r="B62" t="n">
-        <v>86251</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7611,34 +7266,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
+          <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700908</v>
+        <v>700808</v>
       </c>
       <c r="R62" t="n">
-        <v>6391638</v>
+        <v>6391681</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7665,12 +7320,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7681,31 +7341,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120660386</v>
+        <v>117170434</v>
       </c>
       <c r="B63" t="n">
-        <v>86251</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7713,37 +7373,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
+          <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700889</v>
+        <v>700804</v>
       </c>
       <c r="R63" t="n">
-        <v>6391623</v>
+        <v>6391694</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7767,12 +7427,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Alvarglänta i båge mot O, 45 m x 15 m.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7783,83 +7448,69 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>68473004</v>
+        <v>117170437</v>
       </c>
       <c r="B64" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3674</v>
+        <v>221849</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37, Gtl</t>
+          <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700975.4788155581</v>
+        <v>700821</v>
       </c>
       <c r="R64" t="n">
-        <v>6391673.589904672</v>
+        <v>6391712</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7883,22 +7534,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2017-11-25</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2017-11-25</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Alvarglänta 15 m x 5 m.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7907,34 +7553,33 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Amanda Overmark</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Amanda Overmark</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117170356</v>
+        <v>117170454</v>
       </c>
       <c r="B65" t="n">
-        <v>106075</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7966,13 +7611,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>701013</v>
+        <v>700867</v>
       </c>
       <c r="R65" t="n">
-        <v>6391677</v>
+        <v>6391711</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8004,11 +7649,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Undviks vid eventuell avverkning i området.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8020,7 +7660,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhällar.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8038,15 +7678,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117170358</v>
+        <v>117170461</v>
       </c>
       <c r="B66" t="n">
-        <v>103315</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8054,21 +7689,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8078,13 +7713,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>701013</v>
+        <v>700891</v>
       </c>
       <c r="R66" t="n">
-        <v>6391677</v>
+        <v>6391713</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8116,11 +7751,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Undviks vid eventuell avverkning i området.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8132,7 +7762,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhällar.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8150,58 +7780,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120661214</v>
+        <v>117170484</v>
       </c>
       <c r="B67" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>221849</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
+          <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>701034</v>
+        <v>700920</v>
       </c>
       <c r="R67" t="n">
-        <v>6391696</v>
+        <v>6391747</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8225,12 +7845,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8239,22 +7859,2956 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>117170406</v>
+      </c>
+      <c r="B68" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>700839</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6391685</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Alvarglänta 15 m x 10 m i V-O.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>117170322</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>700939</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6391760</v>
+      </c>
+      <c r="S69" t="n">
+        <v>6</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>117170333</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>700959</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6391753</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>117170338</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>700952</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6391748</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>117170341</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>700954</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6391743</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>117170346</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>700963</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6391736</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Alvarmark mot V och norrut mot landsväg.</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>117170348</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>700958</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6391731</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>117170350</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>700953</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6391726</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>117170351</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>700950</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6391720</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>117170352</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>700946</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6391715</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>117170397</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>700759</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6391617</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Minsta antal. Även spridd.</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Sandig glänta i tallskog.</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>117170404</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>700802</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6391676</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Alvarglänta i fuktstråk.</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>117170405</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>700839</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6391685</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Alvarglänta 15 m x 10 m i V-O.</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>117170412</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>700828</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6391684</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>117170417</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>700823</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6391679</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>117170420</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>700818</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6391690</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>117170427</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>700793</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6391685</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. Ansluter till annan glänta mot N. i V-hörn av gläntan.</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>117170485</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>700920</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6391747</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>117170487</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>700917</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6391754</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>117170497</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37, Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>700905</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6391765</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Alvar, kalkhällar.</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>117170457</v>
+      </c>
+      <c r="B88" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>700843</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6391731</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Alvar , kalkkarstspricka.</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>117170467</v>
+      </c>
+      <c r="B89" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>700887</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6391723</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Alvar , kalkkarstspricka.</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>117170441</v>
+      </c>
+      <c r="B90" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>223700</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Hällklofibbla</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Crepis tectorum var. glabrescens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Neuman</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>700821</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6391742</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Karstsprickor 10 cm breda.</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Alvar , kalkkarstspricka vid.</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120660360</v>
+      </c>
+      <c r="B91" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Stadshajden, Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>700881</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6391573</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120660386</v>
+      </c>
+      <c r="B92" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Stadshajden, Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>700889</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6391623</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
+      <c r="AX92" t="inlineStr">
         <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY67" t="inlineStr"/>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120660659</v>
+      </c>
+      <c r="B93" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Stadshajden, Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>700908</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6391638</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17762-2024 artfynd.xlsx
+++ b/artfynd/A 17762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1713,53 +1713,67 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120661214</v>
+        <v>135186893</v>
       </c>
       <c r="B11" t="n">
-        <v>8455</v>
+        <v>43288</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100770</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mindre blåvinge</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cupido minimus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Fuessly, 1775)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701034</v>
+        <v>700891</v>
       </c>
       <c r="R11" t="n">
-        <v>6391696</v>
+        <v>6391712</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,12 +1797,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,78 +1811,87 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117170323</v>
+        <v>135186892</v>
       </c>
       <c r="B12" t="n">
-        <v>99147</v>
+        <v>43304</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219864</v>
+        <v>101260</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700939</v>
+        <v>700888</v>
       </c>
       <c r="R12" t="n">
-        <v>6391760</v>
+        <v>6391691</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1895,12 +1918,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,11 +1934,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1932,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117170330</v>
+        <v>120661214</v>
       </c>
       <c r="B13" t="n">
-        <v>99147</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,51 +1961,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219864</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Stadshajden, Stadshajden, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700967</v>
+        <v>701034</v>
       </c>
       <c r="R13" t="n">
-        <v>6391754</v>
+        <v>6391696</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,17 +2020,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Alvar 40 m x 40 m mot landsväg.</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,30 +2034,26 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117170334</v>
+        <v>117170323</v>
       </c>
       <c r="B14" t="n">
         <v>99147</v>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700959</v>
+        <v>700939</v>
       </c>
       <c r="R14" t="n">
-        <v>6391753</v>
+        <v>6391760</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117170337</v>
+        <v>117170330</v>
       </c>
       <c r="B15" t="n">
         <v>99147</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700952</v>
+        <v>700967</v>
       </c>
       <c r="R15" t="n">
-        <v>6391748</v>
+        <v>6391754</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2254,6 +2254,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Alvar 40 m x 40 m mot landsväg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,7 +2290,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117170345</v>
+        <v>117170334</v>
       </c>
       <c r="B16" t="n">
         <v>99147</v>
@@ -2315,7 +2320,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2334,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700963</v>
+        <v>700959</v>
       </c>
       <c r="R16" t="n">
-        <v>6391736</v>
+        <v>6391753</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2370,11 +2375,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Alvarmark mot V och norrut mot landsväg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,7 +2406,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117170389</v>
+        <v>117170337</v>
       </c>
       <c r="B17" t="n">
         <v>99147</v>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700737</v>
+        <v>700952</v>
       </c>
       <c r="R17" t="n">
-        <v>6391563</v>
+        <v>6391748</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Älväxingglänta övergång mot tallskog på sand.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2522,7 +2522,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117170459</v>
+        <v>117170345</v>
       </c>
       <c r="B18" t="n">
         <v>99147</v>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700872</v>
+        <v>700963</v>
       </c>
       <c r="R18" t="n">
-        <v>6391711</v>
+        <v>6391736</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2607,6 +2607,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Alvarmark mot V och norrut mot landsväg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2638,7 +2643,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117170460</v>
+        <v>117170389</v>
       </c>
       <c r="B19" t="n">
         <v>99147</v>
@@ -2668,7 +2673,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2687,13 +2692,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700880</v>
+        <v>700737</v>
       </c>
       <c r="R19" t="n">
-        <v>6391713</v>
+        <v>6391563</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2736,7 +2741,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Älväxingglänta övergång mot tallskog på sand.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2754,7 +2759,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117170463</v>
+        <v>117170459</v>
       </c>
       <c r="B20" t="n">
         <v>99147</v>
@@ -2803,10 +2808,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700891</v>
+        <v>700872</v>
       </c>
       <c r="R20" t="n">
-        <v>6391713</v>
+        <v>6391711</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2870,7 +2875,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117170471</v>
+        <v>117170460</v>
       </c>
       <c r="B21" t="n">
         <v>99147</v>
@@ -2900,7 +2905,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2919,13 +2924,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700886</v>
+        <v>700880</v>
       </c>
       <c r="R21" t="n">
-        <v>6391729</v>
+        <v>6391713</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2957,11 +2962,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Kalkhällglänta 35 x 10 m.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Alvar , kalkhällglänta.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117170476</v>
+        <v>117170463</v>
       </c>
       <c r="B22" t="n">
         <v>99147</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700894</v>
+        <v>700891</v>
       </c>
       <c r="R22" t="n">
-        <v>6391731</v>
+        <v>6391713</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Alvar , kalkglänta, sand över kalk.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3107,7 +3107,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117170488</v>
+        <v>117170471</v>
       </c>
       <c r="B23" t="n">
         <v>99147</v>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3156,13 +3156,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700917</v>
+        <v>700886</v>
       </c>
       <c r="R23" t="n">
-        <v>6391754</v>
+        <v>6391729</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3194,6 +3194,11 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Kalkhällglänta 35 x 10 m.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3205,7 +3210,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvar , kalkhällglänta.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3223,7 +3228,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117170493</v>
+        <v>117170476</v>
       </c>
       <c r="B24" t="n">
         <v>99147</v>
@@ -3268,14 +3273,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37, Gtl</t>
+          <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700913</v>
+        <v>700894</v>
       </c>
       <c r="R24" t="n">
-        <v>6391766</v>
+        <v>6391731</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3310,11 +3315,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Kalktallskog gles mot S</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvar , kalkglänta, sand över kalk.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117170390</v>
+        <v>117170488</v>
       </c>
       <c r="B25" t="n">
-        <v>99153</v>
+        <v>99147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3355,26 +3355,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>219864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700720</v>
+        <v>700917</v>
       </c>
       <c r="R25" t="n">
-        <v>6391565</v>
+        <v>6391754</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Älväxingglänta övergång mot tallskog på sand.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3460,45 +3460,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117170329</v>
+        <v>117170493</v>
       </c>
       <c r="B26" t="n">
-        <v>104640</v>
+        <v>99147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220164</v>
+        <v>219864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700967</v>
+        <v>700913</v>
       </c>
       <c r="R26" t="n">
-        <v>6391754</v>
+        <v>6391766</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3535,7 +3549,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Alvar 40 m x 40 m mot landsväg.</t>
+          <t>Kalktallskog gles mot S</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3567,45 +3581,59 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117170336</v>
+        <v>117170390</v>
       </c>
       <c r="B27" t="n">
-        <v>104640</v>
+        <v>99153</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220164</v>
+        <v>219874</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700952</v>
+        <v>700720</v>
       </c>
       <c r="R27" t="n">
-        <v>6391748</v>
+        <v>6391565</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3651,7 +3679,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Älväxingglänta övergång mot tallskog på sand.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3669,45 +3697,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117170340</v>
+        <v>135186778</v>
       </c>
       <c r="B28" t="n">
-        <v>104640</v>
+        <v>99233</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220164</v>
+        <v>219875</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700954</v>
+        <v>700824</v>
       </c>
       <c r="R28" t="n">
-        <v>6391743</v>
+        <v>6391714</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3734,12 +3762,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3753,7 +3781,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3771,48 +3799,62 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117170358</v>
+        <v>135186797</v>
       </c>
       <c r="B29" t="n">
-        <v>104640</v>
+        <v>99233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220164</v>
+        <v>219875</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>701013</v>
+        <v>700837</v>
       </c>
       <c r="R29" t="n">
-        <v>6391677</v>
+        <v>6391678</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3836,17 +3878,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Undviks vid eventuell avverkning i området.</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3860,7 +3897,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhällar.</t>
+          <t>Alvar, sand över kalk.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3878,45 +3915,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117170396</v>
+        <v>135186800</v>
       </c>
       <c r="B30" t="n">
-        <v>104640</v>
+        <v>107943</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220164</v>
+        <v>219933</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700743</v>
+        <v>700836</v>
       </c>
       <c r="R30" t="n">
-        <v>6391617</v>
+        <v>6391681</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3943,12 +3980,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3959,6 +3996,11 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Alvar, sand över kalk.</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3975,7 +4017,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117170408</v>
+        <v>117170329</v>
       </c>
       <c r="B31" t="n">
         <v>104640</v>
@@ -4010,10 +4052,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700839</v>
+        <v>700967</v>
       </c>
       <c r="R31" t="n">
-        <v>6391685</v>
+        <v>6391754</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4050,7 +4092,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Alvarglänta 15 m x 10 m i V-O.</t>
+          <t>Alvar 40 m x 40 m mot landsväg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4082,7 +4124,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117170410</v>
+        <v>117170336</v>
       </c>
       <c r="B32" t="n">
         <v>104640</v>
@@ -4117,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700828</v>
+        <v>700952</v>
       </c>
       <c r="R32" t="n">
-        <v>6391684</v>
+        <v>6391748</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4153,11 +4195,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4189,7 +4226,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117170415</v>
+        <v>117170340</v>
       </c>
       <c r="B33" t="n">
         <v>104640</v>
@@ -4224,13 +4261,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700819</v>
+        <v>700954</v>
       </c>
       <c r="R33" t="n">
-        <v>6391683</v>
+        <v>6391743</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4260,11 +4297,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4296,7 +4328,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117170428</v>
+        <v>117170358</v>
       </c>
       <c r="B34" t="n">
         <v>104640</v>
@@ -4331,13 +4363,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700808</v>
+        <v>701013</v>
       </c>
       <c r="R34" t="n">
-        <v>6391681</v>
+        <v>6391677</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4371,7 +4403,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. Ansluter till annan glänta mot N.</t>
+          <t>Undviks vid eventuell avverkning i området.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4385,7 +4417,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvarglänta, kalkhällar.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4403,7 +4435,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117170436</v>
+        <v>117170396</v>
       </c>
       <c r="B35" t="n">
         <v>104640</v>
@@ -4438,10 +4470,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700804</v>
+        <v>700743</v>
       </c>
       <c r="R35" t="n">
-        <v>6391694</v>
+        <v>6391617</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4476,11 +4508,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Alvarglänta i båge mot O, 45 m x 15 m.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4489,11 +4516,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4510,7 +4532,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117170438</v>
+        <v>117170408</v>
       </c>
       <c r="B36" t="n">
         <v>104640</v>
@@ -4545,10 +4567,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700821</v>
+        <v>700839</v>
       </c>
       <c r="R36" t="n">
-        <v>6391712</v>
+        <v>6391685</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4585,7 +4607,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Alvarglänta 15 m x 5 m.</t>
+          <t>Alvarglänta 15 m x 10 m i V-O.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4617,7 +4639,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117170447</v>
+        <v>117170410</v>
       </c>
       <c r="B37" t="n">
         <v>104640</v>
@@ -4652,13 +4674,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700827</v>
+        <v>700828</v>
       </c>
       <c r="R37" t="n">
-        <v>6391746</v>
+        <v>6391684</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4692,7 +4714,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Alvasrglänta på kalk: 15 m x 15 m. Karst i NO.</t>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4724,7 +4746,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117170453</v>
+        <v>117170415</v>
       </c>
       <c r="B38" t="n">
         <v>104640</v>
@@ -4759,13 +4781,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700867</v>
+        <v>700819</v>
       </c>
       <c r="R38" t="n">
-        <v>6391711</v>
+        <v>6391683</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4795,6 +4817,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4826,7 +4853,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117170458</v>
+        <v>117170428</v>
       </c>
       <c r="B39" t="n">
         <v>104640</v>
@@ -4861,13 +4888,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700872</v>
+        <v>700808</v>
       </c>
       <c r="R39" t="n">
-        <v>6391711</v>
+        <v>6391681</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4897,6 +4924,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4928,7 +4960,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117170462</v>
+        <v>117170436</v>
       </c>
       <c r="B40" t="n">
         <v>104640</v>
@@ -4963,10 +4995,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700891</v>
+        <v>700804</v>
       </c>
       <c r="R40" t="n">
-        <v>6391713</v>
+        <v>6391694</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4999,6 +5031,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Alvarglänta i båge mot O, 45 m x 15 m.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5030,7 +5067,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117170470</v>
+        <v>117170438</v>
       </c>
       <c r="B41" t="n">
         <v>104640</v>
@@ -5065,13 +5102,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700886</v>
+        <v>700821</v>
       </c>
       <c r="R41" t="n">
-        <v>6391729</v>
+        <v>6391712</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5105,7 +5142,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Kalkhällglänta 35 x 10 m.</t>
+          <t>Alvarglänta 15 m x 5 m.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5119,7 +5156,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Alvar , kalkhällglänta.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5137,7 +5174,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117170475</v>
+        <v>117170447</v>
       </c>
       <c r="B42" t="n">
         <v>104640</v>
@@ -5172,13 +5209,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700894</v>
+        <v>700827</v>
       </c>
       <c r="R42" t="n">
-        <v>6391731</v>
+        <v>6391746</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5210,6 +5247,11 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Alvasrglänta på kalk: 15 m x 15 m. Karst i NO.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5221,7 +5263,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Alvar , kalkglänta, sand över kalk.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5239,7 +5281,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117170480</v>
+        <v>117170453</v>
       </c>
       <c r="B43" t="n">
         <v>104640</v>
@@ -5274,13 +5316,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700905</v>
+        <v>700867</v>
       </c>
       <c r="R43" t="n">
-        <v>6391738</v>
+        <v>6391711</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5323,7 +5365,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Alvar , kalkglänta, sand över kalk.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5341,7 +5383,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117170486</v>
+        <v>117170458</v>
       </c>
       <c r="B44" t="n">
         <v>104640</v>
@@ -5376,10 +5418,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700917</v>
+        <v>700872</v>
       </c>
       <c r="R44" t="n">
-        <v>6391754</v>
+        <v>6391711</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5443,10 +5485,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117170370</v>
+        <v>117170462</v>
       </c>
       <c r="B45" t="n">
-        <v>110078</v>
+        <v>104640</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5454,21 +5496,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5478,13 +5520,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>700955</v>
+        <v>700891</v>
       </c>
       <c r="R45" t="n">
-        <v>6391666</v>
+        <v>6391713</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5516,11 +5558,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5532,7 +5569,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Sandtallskog.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5550,10 +5587,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117170373</v>
+        <v>117170470</v>
       </c>
       <c r="B46" t="n">
-        <v>110078</v>
+        <v>104640</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5561,21 +5598,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5585,10 +5622,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700948</v>
+        <v>700886</v>
       </c>
       <c r="R46" t="n">
-        <v>6391643</v>
+        <v>6391729</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5625,7 +5662,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Kalkhällglänta 35 x 10 m.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5639,7 +5676,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Sandtallskog.</t>
+          <t>Alvar , kalkhällglänta.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5657,10 +5694,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117170377</v>
+        <v>117170475</v>
       </c>
       <c r="B47" t="n">
-        <v>110078</v>
+        <v>104640</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5668,21 +5705,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5692,13 +5729,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700956</v>
+        <v>700894</v>
       </c>
       <c r="R47" t="n">
-        <v>6391629</v>
+        <v>6391731</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5730,11 +5767,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5746,7 +5778,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Sandtallskog.</t>
+          <t>Alvar , kalkglänta, sand över kalk.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5764,10 +5796,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117170378</v>
+        <v>117170480</v>
       </c>
       <c r="B48" t="n">
-        <v>110078</v>
+        <v>104640</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5775,21 +5807,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5799,10 +5831,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700914</v>
+        <v>700905</v>
       </c>
       <c r="R48" t="n">
-        <v>6391607</v>
+        <v>6391738</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5837,11 +5869,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Enstaka. Pyrola sp. spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5853,7 +5880,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Blåbärstallskog.</t>
+          <t>Alvar , kalkglänta, sand över kalk.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5871,10 +5898,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117170381</v>
+        <v>117170486</v>
       </c>
       <c r="B49" t="n">
-        <v>110078</v>
+        <v>104640</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5882,21 +5909,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5906,13 +5933,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700877</v>
+        <v>700917</v>
       </c>
       <c r="R49" t="n">
-        <v>6391598</v>
+        <v>6391754</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5944,11 +5971,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Enstaka. Pyrola sp. spridd i skogen.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5960,7 +5982,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Blåbärstallskog.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5978,10 +6000,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117170382</v>
+        <v>135186763</v>
       </c>
       <c r="B50" t="n">
-        <v>110078</v>
+        <v>104719</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5989,37 +6011,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700829</v>
+        <v>700891</v>
       </c>
       <c r="R50" t="n">
-        <v>6391575</v>
+        <v>6391748</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6043,17 +6065,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Enstaka. Pyrola sp. spridd i skogen.</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6067,7 +6084,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Blåbärstallskog.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6085,10 +6102,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117170387</v>
+        <v>135186765</v>
       </c>
       <c r="B51" t="n">
-        <v>110078</v>
+        <v>104719</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6096,51 +6113,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700737</v>
+        <v>700837</v>
       </c>
       <c r="R51" t="n">
-        <v>6391563</v>
+        <v>6391761</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6164,17 +6167,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Även spridd i omgivande skog.</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6188,7 +6186,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Tallskog, gammal, på förmodat sandunderlag.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6206,10 +6204,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117170401</v>
+        <v>135186767</v>
       </c>
       <c r="B52" t="n">
-        <v>110078</v>
+        <v>104719</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6217,51 +6215,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700781</v>
+        <v>700838</v>
       </c>
       <c r="R52" t="n">
-        <v>6391656</v>
+        <v>6391741</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6285,12 +6269,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6304,7 +6288,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Tallskog, gammal, på förmodat sandunderlag.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6322,10 +6306,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117170335</v>
+        <v>135186776</v>
       </c>
       <c r="B53" t="n">
-        <v>107517</v>
+        <v>104719</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6333,34 +6317,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700952</v>
+        <v>700824</v>
       </c>
       <c r="R53" t="n">
-        <v>6391748</v>
+        <v>6391714</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6387,12 +6371,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6406,7 +6390,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6424,10 +6408,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117170339</v>
+        <v>135186781</v>
       </c>
       <c r="B54" t="n">
-        <v>107517</v>
+        <v>104719</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6435,34 +6419,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700954</v>
+        <v>700806</v>
       </c>
       <c r="R54" t="n">
-        <v>6391743</v>
+        <v>6391691</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6489,12 +6473,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6508,7 +6492,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6526,10 +6510,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117170343</v>
+        <v>135186801</v>
       </c>
       <c r="B55" t="n">
-        <v>107517</v>
+        <v>104719</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6537,34 +6521,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700963</v>
+        <v>700836</v>
       </c>
       <c r="R55" t="n">
-        <v>6391736</v>
+        <v>6391681</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6591,17 +6575,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Alvarmark mot V och norrut mot landsväg.</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6615,7 +6594,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvar, sand över kalk.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6633,10 +6612,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117170356</v>
+        <v>135186806</v>
       </c>
       <c r="B56" t="n">
-        <v>107517</v>
+        <v>104719</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6644,37 +6623,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>701013</v>
+        <v>700888</v>
       </c>
       <c r="R56" t="n">
-        <v>6391677</v>
+        <v>6391691</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6698,17 +6677,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Undviks vid eventuell avverkning i området.</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6722,7 +6696,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Alvarglänta, kalkhällar.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6740,10 +6714,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117170392</v>
+        <v>135186833</v>
       </c>
       <c r="B57" t="n">
-        <v>107517</v>
+        <v>104719</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6751,34 +6725,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700737</v>
+        <v>700910</v>
       </c>
       <c r="R57" t="n">
-        <v>6391603</v>
+        <v>6391769</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6805,12 +6779,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6821,6 +6795,11 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Alvar.</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -6837,10 +6816,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117170395</v>
+        <v>117170370</v>
       </c>
       <c r="B58" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6848,16 +6827,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6872,13 +6851,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700743</v>
+        <v>700955</v>
       </c>
       <c r="R58" t="n">
-        <v>6391617</v>
+        <v>6391666</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6910,6 +6889,11 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6918,6 +6902,11 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Sandtallskog.</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -6934,10 +6923,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117170409</v>
+        <v>117170373</v>
       </c>
       <c r="B59" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6945,16 +6934,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6969,13 +6958,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700839</v>
+        <v>700948</v>
       </c>
       <c r="R59" t="n">
-        <v>6391685</v>
+        <v>6391643</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7009,7 +6998,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Alvarglänta 15 m x 10 m i V-O. Rikligt.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7023,7 +7012,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Sandtallskog.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7041,10 +7030,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117170411</v>
+        <v>117170377</v>
       </c>
       <c r="B60" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7052,16 +7041,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7076,13 +7065,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700828</v>
+        <v>700956</v>
       </c>
       <c r="R60" t="n">
-        <v>6391684</v>
+        <v>6391629</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7116,7 +7105,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7130,7 +7119,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Sandtallskog.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7148,10 +7137,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117170421</v>
+        <v>117170378</v>
       </c>
       <c r="B61" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7159,16 +7148,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7183,13 +7172,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700818</v>
+        <v>700914</v>
       </c>
       <c r="R61" t="n">
-        <v>6391690</v>
+        <v>6391607</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7223,7 +7212,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+          <t>Enstaka. Pyrola sp. spridd i skogen.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7237,7 +7226,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Blåbärstallskog.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7255,10 +7244,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117170429</v>
+        <v>117170381</v>
       </c>
       <c r="B62" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7266,16 +7255,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7290,10 +7279,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700808</v>
+        <v>700877</v>
       </c>
       <c r="R62" t="n">
-        <v>6391681</v>
+        <v>6391598</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7330,7 +7319,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. Ansluter till annan glänta mot N.</t>
+          <t>Enstaka. Pyrola sp. spridd i skogen.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7344,7 +7333,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Blåbärstallskog.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7362,10 +7351,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117170434</v>
+        <v>117170382</v>
       </c>
       <c r="B63" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7373,16 +7362,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7397,13 +7386,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700804</v>
+        <v>700829</v>
       </c>
       <c r="R63" t="n">
-        <v>6391694</v>
+        <v>6391575</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7437,7 +7426,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Alvarglänta i båge mot O, 45 m x 15 m.</t>
+          <t>Enstaka. Pyrola sp. spridd i skogen.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7451,7 +7440,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Blåbärstallskog.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7469,10 +7458,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117170437</v>
+        <v>117170387</v>
       </c>
       <c r="B64" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7480,16 +7469,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7497,20 +7486,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700821</v>
+        <v>700737</v>
       </c>
       <c r="R64" t="n">
-        <v>6391712</v>
+        <v>6391563</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7544,7 +7547,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Alvarglänta 15 m x 5 m.</t>
+          <t>Även spridd i omgivande skog.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7558,7 +7561,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Tallskog, gammal, på förmodat sandunderlag.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7576,10 +7579,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117170454</v>
+        <v>117170401</v>
       </c>
       <c r="B65" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7587,16 +7590,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7604,20 +7607,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700867</v>
+        <v>700781</v>
       </c>
       <c r="R65" t="n">
-        <v>6391711</v>
+        <v>6391656</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7660,7 +7677,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Tallskog, gammal, på förmodat sandunderlag.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7678,7 +7695,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117170461</v>
+        <v>117170335</v>
       </c>
       <c r="B66" t="n">
         <v>107517</v>
@@ -7713,10 +7730,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700891</v>
+        <v>700952</v>
       </c>
       <c r="R66" t="n">
-        <v>6391713</v>
+        <v>6391748</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7780,7 +7797,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117170484</v>
+        <v>117170339</v>
       </c>
       <c r="B67" t="n">
         <v>107517</v>
@@ -7815,10 +7832,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>700920</v>
+        <v>700954</v>
       </c>
       <c r="R67" t="n">
-        <v>6391747</v>
+        <v>6391743</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7882,10 +7899,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117170406</v>
+        <v>117170343</v>
       </c>
       <c r="B68" t="n">
-        <v>107061</v>
+        <v>107517</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7893,16 +7910,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7917,10 +7934,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700839</v>
+        <v>700963</v>
       </c>
       <c r="R68" t="n">
-        <v>6391685</v>
+        <v>6391736</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7957,7 +7974,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Alvarglänta 15 m x 10 m i V-O.</t>
+          <t>Alvarmark mot V och norrut mot landsväg.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7989,10 +8006,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117170322</v>
+        <v>117170356</v>
       </c>
       <c r="B69" t="n">
-        <v>99781</v>
+        <v>107517</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8000,51 +8017,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700939</v>
+        <v>701013</v>
       </c>
       <c r="R69" t="n">
-        <v>6391760</v>
+        <v>6391677</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8076,6 +8079,11 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Undviks vid eventuell avverkning i området.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8087,7 +8095,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvarglänta, kalkhällar.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8105,10 +8113,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117170333</v>
+        <v>117170392</v>
       </c>
       <c r="B70" t="n">
-        <v>99781</v>
+        <v>107517</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8116,48 +8124,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700959</v>
+        <v>700737</v>
       </c>
       <c r="R70" t="n">
-        <v>6391753</v>
+        <v>6391603</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8200,11 +8194,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8221,10 +8210,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117170338</v>
+        <v>117170395</v>
       </c>
       <c r="B71" t="n">
-        <v>99781</v>
+        <v>107517</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8232,48 +8221,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>700952</v>
+        <v>700743</v>
       </c>
       <c r="R71" t="n">
-        <v>6391748</v>
+        <v>6391617</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8316,11 +8291,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8337,10 +8307,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117170341</v>
+        <v>117170409</v>
       </c>
       <c r="B72" t="n">
-        <v>99781</v>
+        <v>107517</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8348,48 +8318,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>700954</v>
+        <v>700839</v>
       </c>
       <c r="R72" t="n">
-        <v>6391743</v>
+        <v>6391685</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8422,6 +8378,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Alvarglänta 15 m x 10 m i V-O. Rikligt.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8453,10 +8414,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117170346</v>
+        <v>117170411</v>
       </c>
       <c r="B73" t="n">
-        <v>99781</v>
+        <v>107517</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8464,48 +8425,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700963</v>
+        <v>700828</v>
       </c>
       <c r="R73" t="n">
-        <v>6391736</v>
+        <v>6391684</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8542,7 +8489,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Alvarmark mot V och norrut mot landsväg.</t>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8574,10 +8521,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117170348</v>
+        <v>117170421</v>
       </c>
       <c r="B74" t="n">
-        <v>99781</v>
+        <v>107517</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8585,48 +8532,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700958</v>
+        <v>700818</v>
       </c>
       <c r="R74" t="n">
-        <v>6391731</v>
+        <v>6391690</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8659,6 +8592,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8690,10 +8628,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117170350</v>
+        <v>117170429</v>
       </c>
       <c r="B75" t="n">
-        <v>99781</v>
+        <v>107517</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8701,51 +8639,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>700953</v>
+        <v>700808</v>
       </c>
       <c r="R75" t="n">
-        <v>6391726</v>
+        <v>6391681</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8775,6 +8699,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. Ansluter till annan glänta mot N.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8806,10 +8735,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117170351</v>
+        <v>117170434</v>
       </c>
       <c r="B76" t="n">
-        <v>99781</v>
+        <v>107517</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8817,51 +8746,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700950</v>
+        <v>700804</v>
       </c>
       <c r="R76" t="n">
-        <v>6391720</v>
+        <v>6391694</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8891,6 +8806,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Alvarglänta i båge mot O, 45 m x 15 m.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8922,10 +8842,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117170352</v>
+        <v>117170437</v>
       </c>
       <c r="B77" t="n">
-        <v>99781</v>
+        <v>107517</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8933,48 +8853,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700946</v>
+        <v>700821</v>
       </c>
       <c r="R77" t="n">
-        <v>6391715</v>
+        <v>6391712</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9007,6 +8913,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Alvarglänta 15 m x 5 m.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9038,10 +8949,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117170397</v>
+        <v>117170454</v>
       </c>
       <c r="B78" t="n">
-        <v>99781</v>
+        <v>107517</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9049,51 +8960,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700759</v>
+        <v>700867</v>
       </c>
       <c r="R78" t="n">
-        <v>6391617</v>
+        <v>6391711</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9125,11 +9022,6 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Minsta antal. Även spridd.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9141,7 +9033,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Sandig glänta i tallskog.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9159,10 +9051,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117170404</v>
+        <v>117170461</v>
       </c>
       <c r="B79" t="n">
-        <v>99781</v>
+        <v>107517</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9170,48 +9062,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Endre Bäcks 1:37., Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700802</v>
+        <v>700891</v>
       </c>
       <c r="R79" t="n">
-        <v>6391676</v>
+        <v>6391713</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9257,7 +9135,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Alvarglänta i fuktstråk.</t>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9275,10 +9153,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117170405</v>
+        <v>117170484</v>
       </c>
       <c r="B80" t="n">
-        <v>99781</v>
+        <v>107517</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9286,21 +9164,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9310,10 +9188,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700839</v>
+        <v>700920</v>
       </c>
       <c r="R80" t="n">
-        <v>6391685</v>
+        <v>6391747</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9346,11 +9224,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Alvarglänta 15 m x 10 m i V-O.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9382,10 +9255,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117170412</v>
+        <v>135186764</v>
       </c>
       <c r="B81" t="n">
-        <v>99781</v>
+        <v>107598</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9393,48 +9266,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700828</v>
+        <v>700891</v>
       </c>
       <c r="R81" t="n">
-        <v>6391684</v>
+        <v>6391748</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9461,17 +9320,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9485,7 +9339,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9503,10 +9357,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117170417</v>
+        <v>135186766</v>
       </c>
       <c r="B82" t="n">
-        <v>99781</v>
+        <v>107598</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9514,34 +9368,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700823</v>
+        <v>700837</v>
       </c>
       <c r="R82" t="n">
-        <v>6391679</v>
+        <v>6391761</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9568,17 +9422,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9592,7 +9441,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9610,10 +9459,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117170420</v>
+        <v>135186768</v>
       </c>
       <c r="B83" t="n">
-        <v>99781</v>
+        <v>107598</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9621,34 +9470,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700818</v>
+        <v>700838</v>
       </c>
       <c r="R83" t="n">
-        <v>6391690</v>
+        <v>6391741</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9675,17 +9524,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9699,7 +9543,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9717,10 +9561,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117170427</v>
+        <v>135186773</v>
       </c>
       <c r="B84" t="n">
-        <v>99781</v>
+        <v>107598</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9728,51 +9572,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>700793</v>
+        <v>700824</v>
       </c>
       <c r="R84" t="n">
-        <v>6391685</v>
+        <v>6391714</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9796,17 +9626,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Alvarglänta 50 m x 20 m i V-O. Ansluter till annan glänta mot N. i V-hörn av gläntan.</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9820,7 +9645,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9838,10 +9663,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117170485</v>
+        <v>135186779</v>
       </c>
       <c r="B85" t="n">
-        <v>99781</v>
+        <v>107598</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9849,48 +9674,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>700920</v>
+        <v>700806</v>
       </c>
       <c r="R85" t="n">
-        <v>6391747</v>
+        <v>6391691</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9917,12 +9728,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9936,7 +9747,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9954,10 +9765,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117170487</v>
+        <v>135186791</v>
       </c>
       <c r="B86" t="n">
-        <v>99781</v>
+        <v>107598</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9965,48 +9776,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>700917</v>
+        <v>700816</v>
       </c>
       <c r="R86" t="n">
-        <v>6391754</v>
+        <v>6391680</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10033,12 +9830,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10052,7 +9849,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+          <t>Alvar, vätartad glänta.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10070,10 +9867,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117170497</v>
+        <v>135186795</v>
       </c>
       <c r="B87" t="n">
-        <v>99781</v>
+        <v>107598</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10081,48 +9878,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37, Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>700905</v>
+        <v>700837</v>
       </c>
       <c r="R87" t="n">
-        <v>6391765</v>
+        <v>6391678</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10149,12 +9932,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10168,7 +9951,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Alvar, kalkhällar.</t>
+          <t>Alvar, sand över kalk.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10186,45 +9969,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117170457</v>
+        <v>135186802</v>
       </c>
       <c r="B88" t="n">
-        <v>101326</v>
+        <v>107598</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222498</v>
+        <v>221849</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>700843</v>
+        <v>700836</v>
       </c>
       <c r="R88" t="n">
-        <v>6391731</v>
+        <v>6391681</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10251,12 +10034,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10270,7 +10053,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Alvar , kalkkarstspricka.</t>
+          <t>Alvar, sand över kalk.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10288,48 +10071,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117170467</v>
+        <v>135186808</v>
       </c>
       <c r="B89" t="n">
-        <v>101326</v>
+        <v>107598</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>221849</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>700887</v>
+        <v>700888</v>
       </c>
       <c r="R89" t="n">
-        <v>6391723</v>
+        <v>6391691</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10353,12 +10136,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10372,7 +10155,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Alvar , kalkkarstspricka.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10390,10 +10173,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117170441</v>
+        <v>135186811</v>
       </c>
       <c r="B90" t="n">
-        <v>108205</v>
+        <v>107598</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10401,48 +10184,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>223700</v>
+        <v>221849</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hällklofibbla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Crepis tectorum var. glabrescens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Neuman</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Endre Bäcks 1:37., Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>700821</v>
+        <v>700891</v>
       </c>
       <c r="R90" t="n">
-        <v>6391742</v>
+        <v>6391712</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10469,17 +10238,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Karstsprickor 10 cm breda.</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10493,7 +10257,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Alvar , kalkkarstspricka vid.</t>
+          <t>Alvarskog, gles med gläntor.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10511,10 +10275,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120660360</v>
+        <v>135186814</v>
       </c>
       <c r="B91" t="n">
-        <v>87346</v>
+        <v>107598</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10522,37 +10286,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>700881</v>
+        <v>700896</v>
       </c>
       <c r="R91" t="n">
-        <v>6391573</v>
+        <v>6391730</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10576,22 +10340,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10602,26 +10356,31 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Alvarskog, gles med gläntor.</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120660386</v>
+        <v>135186823</v>
       </c>
       <c r="B92" t="n">
-        <v>87346</v>
+        <v>107598</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10629,37 +10388,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>700889</v>
+        <v>700952</v>
       </c>
       <c r="R92" t="n">
-        <v>6391623</v>
+        <v>6391719</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10683,12 +10442,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10699,26 +10458,31 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>Alvar, sand över kalk.</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120660659</v>
+        <v>135186844</v>
       </c>
       <c r="B93" t="n">
-        <v>87346</v>
+        <v>107598</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10726,37 +10490,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>700908</v>
+        <v>700910</v>
       </c>
       <c r="R93" t="n">
-        <v>6391638</v>
+        <v>6391769</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10780,12 +10544,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10796,19 +10560,3582 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Alvar.</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>117170406</v>
+      </c>
+      <c r="B94" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>700839</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6391685</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Alvarglänta 15 m x 10 m i V-O.</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>117170322</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>700939</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6391760</v>
+      </c>
+      <c r="S95" t="n">
+        <v>6</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>117170333</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>700959</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6391753</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>117170338</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>700952</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6391748</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>117170341</v>
+      </c>
+      <c r="B98" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>700954</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6391743</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>117170346</v>
+      </c>
+      <c r="B99" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>700963</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6391736</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Alvarmark mot V och norrut mot landsväg.</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>117170348</v>
+      </c>
+      <c r="B100" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>700958</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6391731</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>117170350</v>
+      </c>
+      <c r="B101" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>700953</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6391726</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>117170351</v>
+      </c>
+      <c r="B102" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>700950</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6391720</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>117170352</v>
+      </c>
+      <c r="B103" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>700946</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6391715</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>117170397</v>
+      </c>
+      <c r="B104" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>700759</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6391617</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Minsta antal. Även spridd.</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Sandig glänta i tallskog.</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>117170404</v>
+      </c>
+      <c r="B105" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>700802</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6391676</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Alvarglänta i fuktstråk.</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>117170405</v>
+      </c>
+      <c r="B106" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>700839</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6391685</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Alvarglänta 15 m x 10 m i V-O.</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>117170412</v>
+      </c>
+      <c r="B107" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>700828</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6391684</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>117170417</v>
+      </c>
+      <c r="B108" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>700823</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6391679</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>117170420</v>
+      </c>
+      <c r="B109" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>700818</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6391690</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. I O-del. Ansluter till annan glänta mot N.</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>117170427</v>
+      </c>
+      <c r="B110" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>700793</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6391685</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Alvarglänta 50 m x 20 m i V-O. Ansluter till annan glänta mot N. i V-hörn av gläntan.</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>117170485</v>
+      </c>
+      <c r="B111" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>700920</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6391747</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>117170487</v>
+      </c>
+      <c r="B112" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>700917</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6391754</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Alvar i gläntor i gles alvarskog med tall och enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>117170497</v>
+      </c>
+      <c r="B113" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37, Gtl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>700905</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6391765</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Alvar, kalkhällar.</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>135186774</v>
+      </c>
+      <c r="B114" t="n">
+        <v>99858</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>700824</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6391714</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>Alvarskog, gles med gläntor.</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>135186780</v>
+      </c>
+      <c r="B115" t="n">
+        <v>99858</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>700806</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6391691</v>
+      </c>
+      <c r="S115" t="n">
+        <v>5</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>Alvarskog, gles med gläntor.</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>135186805</v>
+      </c>
+      <c r="B116" t="n">
+        <v>99858</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>700888</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6391691</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>Alvarskog, gles med gläntor.</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>135186821</v>
+      </c>
+      <c r="B117" t="n">
+        <v>99858</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>700952</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6391719</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>Alvar, sand över kalk.</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117170457</v>
+      </c>
+      <c r="B118" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>700843</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6391731</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>Alvar , kalkkarstspricka.</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117170467</v>
+      </c>
+      <c r="B119" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>700887</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6391723</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>Alvar , kalkkarstspricka.</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>135186771</v>
+      </c>
+      <c r="B120" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>700843</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6391734</v>
+      </c>
+      <c r="S120" t="n">
+        <v>5</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>Karsthällmark, i karst.</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>117170441</v>
+      </c>
+      <c r="B121" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>223700</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Hällklofibbla</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Crepis tectorum var. glabrescens</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Neuman</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37., Gtl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>700821</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6391742</v>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Karstsprickor 10 cm breda.</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>Alvar , kalkkarstspricka vid.</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>135186798</v>
+      </c>
+      <c r="B122" t="n">
+        <v>106466</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>224190</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Flockarun</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Centaurium erythraea var. erythraea</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Endre Bäcks 1:37 A 17764-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>700837</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6391678</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>Alvar, sand över kalk.</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>120660360</v>
+      </c>
+      <c r="B123" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Stadshajden, Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>700881</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6391573</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>120660386</v>
+      </c>
+      <c r="B124" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Stadshajden, Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>700889</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6391623</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
+      <c r="AX124" t="inlineStr">
         <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY93" t="inlineStr"/>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>120660659</v>
+      </c>
+      <c r="B125" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Stadshajden, Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>700908</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6391638</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17762-2024 artfynd.xlsx
+++ b/artfynd/A 17762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY125"/>
+  <dimension ref="A1:AZ125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>NMC - Nordic Mycological Congress</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/213815</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>NMC - Nordic Mycological Congress</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/233570</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170372</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1142,6 +1162,11 @@
           <t>NMC - Nordic Mycological Congress</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1088797</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1249,6 +1274,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170418</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170419</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1486,6 +1521,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170492</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,6 +1638,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68473004</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1710,6 +1755,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68473016</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1826,6 +1876,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186893</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1947,6 +2002,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186892</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2050,6 +2110,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120661214</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2166,6 +2231,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170323</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2287,6 +2357,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170330</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2403,6 +2478,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170334</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2519,6 +2599,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170337</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2640,6 +2725,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170345</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2756,6 +2846,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170389</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2872,6 +2967,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170459</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2988,6 +3088,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170460</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3104,6 +3209,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170463</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3225,6 +3335,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170471</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3341,6 +3456,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170476</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3457,6 +3577,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170488</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3578,6 +3703,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170493</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3694,6 +3824,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170390</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3796,6 +3931,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186778</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3912,6 +4052,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186797</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4014,6 +4159,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186800</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4121,6 +4271,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170329</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4223,6 +4378,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170336</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4325,6 +4485,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170340</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4432,6 +4597,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170358</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4529,6 +4699,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170396</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4636,6 +4811,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170408</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4743,6 +4923,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170410</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4850,6 +5035,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170415</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4957,6 +5147,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170428</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5064,6 +5259,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170436</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5171,6 +5371,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170438</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5278,6 +5483,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170447</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5380,6 +5590,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170453</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5482,6 +5697,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170458</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5584,6 +5804,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170462</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5691,6 +5916,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170470</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5793,6 +6023,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170475</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5895,6 +6130,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170480</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5997,6 +6237,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170486</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6099,6 +6344,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186763</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6201,6 +6451,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186765</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6303,6 +6558,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186767</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6405,6 +6665,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186776</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6507,6 +6772,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186781</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6609,6 +6879,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186801</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6711,6 +6986,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186806</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6813,6 +7093,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186833</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6920,6 +7205,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170370</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7027,6 +7317,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170373</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7134,6 +7429,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170377</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7241,6 +7541,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170378</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7348,6 +7653,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170381</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7455,6 +7765,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170382</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7576,6 +7891,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170387</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7692,6 +8012,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170401</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7794,6 +8119,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170335</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7896,6 +8226,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170339</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8003,6 +8338,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170343</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8110,6 +8450,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170356</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8207,6 +8552,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170392</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8304,6 +8654,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170395</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8411,6 +8766,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170409</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8518,6 +8878,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170411</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8625,6 +8990,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170421</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8732,6 +9102,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170429</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8839,6 +9214,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170434</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8946,6 +9326,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170437</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9048,6 +9433,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170454</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9150,6 +9540,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170461</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9252,6 +9647,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170484</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9354,6 +9754,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186764</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9456,6 +9861,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186766</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9558,6 +9968,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186768</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9660,6 +10075,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186773</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9762,6 +10182,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186779</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9864,6 +10289,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186791</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9966,6 +10396,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186795</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10068,6 +10503,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186802</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10170,6 +10610,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186808</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10272,6 +10717,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186811</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10374,6 +10824,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186814</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10476,6 +10931,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186823</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10578,6 +11038,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186844</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10685,6 +11150,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170406</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10801,6 +11271,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170322</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10917,6 +11392,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170333</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11033,6 +11513,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170338</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11149,6 +11634,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170341</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11270,6 +11760,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170346</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11386,6 +11881,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170348</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11502,6 +12002,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170350</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11618,6 +12123,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170351</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11734,6 +12244,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170352</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11855,6 +12370,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170397</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11971,6 +12491,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170404</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12078,6 +12603,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170405</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12199,6 +12729,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170412</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12306,6 +12841,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170417</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12413,6 +12953,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170420</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12534,6 +13079,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170427</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12650,6 +13200,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170485</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12766,6 +13321,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170487</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12882,6 +13442,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170497</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12984,6 +13549,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186774</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13086,6 +13656,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186780</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13193,6 +13768,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186805</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13296,6 +13876,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186821</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13398,6 +13983,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170457</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13500,6 +14090,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170467</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13602,6 +14197,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186771</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13723,6 +14323,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117170441</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13835,6 +14440,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135186798</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13942,6 +14552,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120660360</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14039,6 +14654,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120660386</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14136,8 +14756,139 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120660659</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 17762-2024 artfynd.xlsx
+++ b/artfynd/A 17762-2024 artfynd.xlsx
@@ -1766,7 +1766,7 @@
         <v>135186893</v>
       </c>
       <c r="B11" t="n">
-        <v>43288</v>
+        <v>43293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>135186892</v>
       </c>
       <c r="B12" t="n">
-        <v>43304</v>
+        <v>43309</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>135186778</v>
       </c>
       <c r="B28" t="n">
-        <v>99233</v>
+        <v>99280</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>135186797</v>
       </c>
       <c r="B29" t="n">
-        <v>99233</v>
+        <v>99280</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>135186800</v>
       </c>
       <c r="B30" t="n">
-        <v>107943</v>
+        <v>107998</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>135186763</v>
       </c>
       <c r="B50" t="n">
-        <v>104719</v>
+        <v>104773</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>135186765</v>
       </c>
       <c r="B51" t="n">
-        <v>104719</v>
+        <v>104773</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>135186767</v>
       </c>
       <c r="B52" t="n">
-        <v>104719</v>
+        <v>104773</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>135186776</v>
       </c>
       <c r="B53" t="n">
-        <v>104719</v>
+        <v>104773</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>135186781</v>
       </c>
       <c r="B54" t="n">
-        <v>104719</v>
+        <v>104773</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>135186801</v>
       </c>
       <c r="B55" t="n">
-        <v>104719</v>
+        <v>104773</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>135186806</v>
       </c>
       <c r="B56" t="n">
-        <v>104719</v>
+        <v>104773</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>135186833</v>
       </c>
       <c r="B57" t="n">
-        <v>104719</v>
+        <v>104773</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>135186764</v>
       </c>
       <c r="B81" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>135186766</v>
       </c>
       <c r="B82" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>135186768</v>
       </c>
       <c r="B83" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>135186773</v>
       </c>
       <c r="B84" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>135186779</v>
       </c>
       <c r="B85" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>135186791</v>
       </c>
       <c r="B86" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>135186795</v>
       </c>
       <c r="B87" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>135186802</v>
       </c>
       <c r="B88" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>135186808</v>
       </c>
       <c r="B89" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>135186811</v>
       </c>
       <c r="B90" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>135186814</v>
       </c>
       <c r="B91" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>135186823</v>
       </c>
       <c r="B92" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>135186844</v>
       </c>
       <c r="B93" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>135186774</v>
       </c>
       <c r="B114" t="n">
-        <v>99858</v>
+        <v>99905</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>135186780</v>
       </c>
       <c r="B115" t="n">
-        <v>99858</v>
+        <v>99905</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>135186805</v>
       </c>
       <c r="B116" t="n">
-        <v>99858</v>
+        <v>99905</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>135186821</v>
       </c>
       <c r="B117" t="n">
-        <v>99858</v>
+        <v>99905</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>135186771</v>
       </c>
       <c r="B120" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>135186798</v>
       </c>
       <c r="B122" t="n">
-        <v>106466</v>
+        <v>106521</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 17762-2024 artfynd.xlsx
+++ b/artfynd/A 17762-2024 artfynd.xlsx
@@ -3835,7 +3835,7 @@
         <v>135186778</v>
       </c>
       <c r="B28" t="n">
-        <v>99280</v>
+        <v>99307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>135186797</v>
       </c>
       <c r="B29" t="n">
-        <v>99280</v>
+        <v>99307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>135186800</v>
       </c>
       <c r="B30" t="n">
-        <v>107998</v>
+        <v>108025</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>135186763</v>
       </c>
       <c r="B50" t="n">
-        <v>104773</v>
+        <v>104800</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>135186765</v>
       </c>
       <c r="B51" t="n">
-        <v>104773</v>
+        <v>104800</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>135186767</v>
       </c>
       <c r="B52" t="n">
-        <v>104773</v>
+        <v>104800</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>135186776</v>
       </c>
       <c r="B53" t="n">
-        <v>104773</v>
+        <v>104800</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>135186781</v>
       </c>
       <c r="B54" t="n">
-        <v>104773</v>
+        <v>104800</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>135186801</v>
       </c>
       <c r="B55" t="n">
-        <v>104773</v>
+        <v>104800</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>135186806</v>
       </c>
       <c r="B56" t="n">
-        <v>104773</v>
+        <v>104800</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>135186833</v>
       </c>
       <c r="B57" t="n">
-        <v>104773</v>
+        <v>104800</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>135186764</v>
       </c>
       <c r="B81" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>135186766</v>
       </c>
       <c r="B82" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>135186768</v>
       </c>
       <c r="B83" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>135186773</v>
       </c>
       <c r="B84" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>135186779</v>
       </c>
       <c r="B85" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>135186791</v>
       </c>
       <c r="B86" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>135186795</v>
       </c>
       <c r="B87" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>135186802</v>
       </c>
       <c r="B88" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>135186808</v>
       </c>
       <c r="B89" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>135186811</v>
       </c>
       <c r="B90" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>135186814</v>
       </c>
       <c r="B91" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>135186823</v>
       </c>
       <c r="B92" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>135186844</v>
       </c>
       <c r="B93" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>135186774</v>
       </c>
       <c r="B114" t="n">
-        <v>99905</v>
+        <v>99932</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>135186780</v>
       </c>
       <c r="B115" t="n">
-        <v>99905</v>
+        <v>99932</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>135186805</v>
       </c>
       <c r="B116" t="n">
-        <v>99905</v>
+        <v>99932</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>135186821</v>
       </c>
       <c r="B117" t="n">
-        <v>99905</v>
+        <v>99932</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>135186771</v>
       </c>
       <c r="B120" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>135186798</v>
       </c>
       <c r="B122" t="n">
-        <v>106521</v>
+        <v>106548</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
